--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486722_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486722_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3108</v>
+        <v>8.6982</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2718</v>
+        <v>3.4786</v>
       </c>
       <c r="F2" t="n">
-        <v>6.039</v>
+        <v>5.2195</v>
       </c>
       <c r="G2" t="n">
         <v>4.4841</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>2.599</v>
+        <v>1.9863</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8823</v>
+        <v>1.0892</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7166</v>
+        <v>0.8972</v>
       </c>
       <c r="V2" t="n">
         <v>1.8415</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.6173</v>
+        <v>8.5305</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9591</v>
+        <v>4.6489</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6581</v>
+        <v>3.8816</v>
       </c>
       <c r="G3" t="n">
         <v>7.7856</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8937</v>
+        <v>0.8069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.5169</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0665</v>
+        <v>0.29</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0273</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>A. LOPEZ ROMERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9894</v>
+        <v>7.326</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2744</v>
+        <v>3.0099</v>
       </c>
       <c r="F4" t="n">
-        <v>1.715</v>
+        <v>4.3161</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1508</v>
+        <v>4.2089</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4207</v>
+        <v>2.7304</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7302</v>
+        <v>1.4785</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7722</v>
+        <v>2.2791</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7315</v>
+        <v>2.3175</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0407</v>
+        <v>-0.0384</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3786</v>
+        <v>1.9298</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6892</v>
+        <v>0.4129</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6895</v>
+        <v>1.5169</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3832</v>
+        <v>0.1863</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7925</v>
+        <v>0.117</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5906</v>
+        <v>0.0694</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8415</v>
+        <v>0.6138</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6404</v>
+        <v>0.6138</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LOPEZ ROMERA</t>
+          <t>L. BULASHVILI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.9813</v>
+        <v>6.4157</v>
       </c>
       <c r="E5" t="n">
-        <v>2.286</v>
+        <v>5.1297</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6953</v>
+        <v>1.286</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2089</v>
+        <v>5.2062</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7304</v>
+        <v>4.5867</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4785</v>
+        <v>0.6194</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2791</v>
+        <v>5.131</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3175</v>
+        <v>5.2078</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0384</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9298</v>
+        <v>0.0752</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4129</v>
+        <v>-0.6211</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5169</v>
+        <v>0.6962</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3169</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1584</v>
+        <v>0.5724</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.607</v>
+        <v>0.3929</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5514</v>
+        <v>0.1795</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6138</v>
+        <v>-0.3282</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6138</v>
+        <v>0.5712</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BULASHVILI</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.3689</v>
+        <v>5.8062</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4057</v>
+        <v>4.2402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9631999999999999</v>
+        <v>1.566</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2062</v>
+        <v>3.1508</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5867</v>
+        <v>2.4207</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6194</v>
+        <v>0.7302</v>
       </c>
       <c r="J6" t="n">
-        <v>5.131</v>
+        <v>1.7722</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2078</v>
+        <v>1.7315</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0752</v>
+        <v>1.3786</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6211</v>
+        <v>0.6892</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6962</v>
+        <v>0.6895</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4744</v>
+        <v>1.1999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>0.7583</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1433</v>
+        <v>0.4416</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3282</v>
+        <v>1.8415</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5712</v>
+        <v>3.6404</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8995</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>L. BUENO CASTILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6247</v>
+        <v>3.8871</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4574</v>
+        <v>0.2537</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1672</v>
+        <v>3.6334</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2365</v>
+        <v>3.2673</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5652</v>
+        <v>4.6553</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8017</v>
+        <v>-1.388</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4375</v>
+        <v>2.1581</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7457</v>
+        <v>4.794</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6918</v>
+        <v>-2.6358</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2009</v>
+        <v>1.1092</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3109</v>
+        <v>-0.1387</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1099</v>
+        <v>1.2478</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3862</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9167</v>
+        <v>1.1725</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9508</v>
+        <v>0.7721</v>
       </c>
       <c r="U7" t="n">
-        <v>0.966</v>
+        <v>0.4004</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1424</v>
+        <v>1.1851</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. BUENO CASTILLO</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5976</v>
+        <v>1.8264</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.16</v>
+        <v>-0.3108</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7576</v>
+        <v>2.1373</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2673</v>
+        <v>1.8264</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6553</v>
+        <v>0.6825</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.388</v>
+        <v>1.1439</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1581</v>
+        <v>1.5512</v>
       </c>
       <c r="K8" t="n">
-        <v>4.794</v>
+        <v>1.5105</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6358</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1092</v>
+        <v>0.2752</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1387</v>
+        <v>-0.828</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2478</v>
+        <v>1.1032</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7377</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.883</v>
+        <v>0.1931</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>0.0687</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5246</v>
+        <v>0.1244</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1314</v>
+        <v>1.3699</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9314</v>
+        <v>0.6993</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0628</v>
+        <v>0.6706</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8264</v>
+        <v>1.2365</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6825</v>
+        <v>-0.5652</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1439</v>
+        <v>1.8017</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5512</v>
+        <v>1.4375</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5105</v>
+        <v>0.7457</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>0.6918</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2752</v>
+        <v>-0.2009</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.828</v>
+        <v>-1.3109</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1032</v>
+        <v>1.1099</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5019</v>
+        <v>1.6619</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>1.1926</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0499</v>
+        <v>0.4693</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.1424</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1424</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2512</v>
+        <v>-1.0236</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2485</v>
+        <v>0.3519</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4997</v>
+        <v>-1.3755</v>
       </c>
       <c r="G10" t="n">
         <v>0.1101</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1103</v>
+        <v>0.1173</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0551</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6717</v>
+        <v>-2.138</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6477</v>
+        <v>-3.3375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.976</v>
+        <v>1.1995</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0002</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7062</v>
+        <v>-0.1724</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4415</v>
+        <v>-0.1312</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2647</v>
+        <v>-0.0412</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>40.6985</v>
+        <v>40.6984</v>
       </c>
       <c r="E12" t="n">
-        <v>18.1638</v>
+        <v>18.1639</v>
       </c>
       <c r="F12" t="n">
         <v>22.5345</v>
@@ -1360,7 +1360,7 @@
         <v>23.4484</v>
       </c>
       <c r="I12" t="n">
-        <v>6.827199999999999</v>
+        <v>6.8272</v>
       </c>
       <c r="J12" t="n">
         <v>22.6638</v>
@@ -1381,7 +1381,7 @@
         <v>9.686500000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999932285e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.3772</v>
@@ -1390,13 +1390,13 @@
         <v>17.377</v>
       </c>
       <c r="S12" t="n">
-        <v>7.7244</v>
+        <v>7.7242</v>
       </c>
       <c r="T12" t="n">
-        <v>4.824499999999999</v>
+        <v>4.8247</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8997</v>
+        <v>2.8996</v>
       </c>
       <c r="V12" t="n">
         <v>2.6984</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6196</v>
+        <v>-2.5889</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6824</v>
+        <v>-3.4336</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9372</v>
+        <v>0.8446</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.621</v>
+        <v>-2.4273</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8072</v>
+        <v>-1.5999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8138</v>
+        <v>-0.8274</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9444</v>
+        <v>-0.9784</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2549</v>
+        <v>0.4006</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6895</v>
+        <v>-1.379</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6766</v>
+        <v>-1.4489</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.5522</v>
+        <v>-2.0005</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1244</v>
+        <v>0.5516</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7723</v>
+        <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4965</v>
+        <v>-0.4553</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1928</v>
+        <v>-0.5244</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6894</v>
+        <v>0.0692</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8842</v>
+        <v>-0.2856</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.0955</v>
+        <v>-2.9176</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1989</v>
+        <v>-2.1926</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8965</v>
+        <v>-0.725</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5793</v>
+        <v>-3.9311</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4753</v>
+        <v>-1.7315</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.104</v>
+        <v>-2.1996</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0289</v>
+        <v>-1.6612</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8359</v>
+        <v>1.0967</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-2.7579</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6082</v>
+        <v>-2.2698</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.3112</v>
+        <v>-2.8282</v>
       </c>
       <c r="O14" t="n">
-        <v>0.703</v>
+        <v>0.5583</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3862</v>
+        <v>1.9308</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7031</v>
+        <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4412</v>
+        <v>-0.9173</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6337</v>
+        <v>-0.5314</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1925</v>
+        <v>-0.3859</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.1268</v>
+        <v>-2.9298</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.8473</v>
+        <v>-0.9926</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7205</v>
+        <v>-1.9372</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4273</v>
+        <v>-3.621</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5999</v>
+        <v>-2.8072</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8274</v>
+        <v>-0.8138</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9784</v>
+        <v>-0.9444</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4006</v>
+        <v>-0.2549</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.379</v>
+        <v>-0.6895</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4489</v>
+        <v>-2.6766</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.0005</v>
+        <v>-2.5522</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5516</v>
+        <v>-0.1244</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>2.51</v>
+        <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9931</v>
+        <v>-0.8068</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9381</v>
+        <v>-0.1174</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.055</v>
+        <v>-0.6894</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2856</v>
+        <v>1.8842</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.4225</v>
+        <v>-3.4184</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5252</v>
+        <v>-0.4218</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.8973</v>
+        <v>-2.9966</v>
       </c>
       <c r="G16" t="n">
         <v>-2.504</v>
@@ -1702,13 +1702,13 @@
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5903</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6622</v>
+        <v>-0.5588</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0274</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3282</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.4232</v>
+        <v>-3.663</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2072</v>
+        <v>-2.6209</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2159</v>
+        <v>-1.0421</v>
       </c>
       <c r="G17" t="n">
         <v>-3.9389</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1327</v>
+        <v>-0.3726</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4409</v>
+        <v>0.0272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5736</v>
+        <v>-0.3998</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.534</v>
+        <v>-4.0786</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7097</v>
+        <v>-2.1138</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8243</v>
+        <v>-1.9648</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.9311</v>
+        <v>-0.5865</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7315</v>
+        <v>-0.3175</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1996</v>
+        <v>-0.269</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6612</v>
+        <v>0.9932</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0967</v>
+        <v>0.9932</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.7579</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2698</v>
+        <v>-1.5797</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.8282</v>
+        <v>-1.3107</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5583</v>
+        <v>-0.269</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9308</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.0546</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5337</v>
+        <v>-0.1172</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0485</v>
+        <v>0.0481</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4852</v>
+        <v>-0.1654</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9173</v>
+        <v>-4.3161</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8036</v>
+        <v>-1.9229</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1138</v>
+        <v>-2.3932</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5865</v>
+        <v>-2.5793</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3175</v>
+        <v>-2.4753</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.269</v>
+        <v>-0.104</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9932</v>
+        <v>0.0289</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9932</v>
+        <v>0.8359</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5797</v>
+        <v>-2.6082</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3107</v>
+        <v>-3.3112</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.269</v>
+        <v>0.703</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.3862</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-3.0892</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-4.0546</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.9654</v>
+        <v>2.7031</v>
       </c>
       <c r="S19" t="n">
-        <v>0.044</v>
+        <v>-0.7794</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3584</v>
+        <v>-0.0902</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3144</v>
+        <v>-0.6891</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2856</v>
+        <v>-0.5712</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8995</v>
+        <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1851</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9558</v>
+        <v>-5.4941</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.567</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3888</v>
+        <v>-4.549</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.728</v>
+        <v>-1.9036</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.5305</v>
+        <v>-1.1305</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8025</v>
+        <v>-0.7732</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3958</v>
+        <v>1.1182</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3573</v>
+        <v>2.4565</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0384</v>
+        <v>-1.3383</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3323</v>
+        <v>-3.0219</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.1732</v>
+        <v>-3.587</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8409</v>
+        <v>0.5651</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>2.1239</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.309</v>
+        <v>-1.6138</v>
       </c>
       <c r="T20" t="n">
-        <v>0.165</v>
+        <v>-0.7038</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.474</v>
+        <v>-0.91</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2703</v>
+        <v>-2.1698</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3709</v>
+        <v>0.5712</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8995</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2905</v>
+        <v>-5.564</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4275</v>
+        <v>-3.8773</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8629</v>
+        <v>-1.6867</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.0559</v>
+        <v>-4.728</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3175</v>
+        <v>-5.5305</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7384</v>
+        <v>0.8025</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5517</v>
+        <v>-2.3958</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5239</v>
+        <v>-2.3573</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0277</v>
+        <v>-0.0384</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5043</v>
+        <v>-2.3323</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7936</v>
+        <v>-3.1732</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2893</v>
+        <v>0.8409</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>1.3515</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5446</v>
+        <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7212</v>
+        <v>-0.9173</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7174</v>
+        <v>-0.1453</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0038</v>
+        <v>-0.772</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8995</v>
+        <v>-1.2703</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X21" t="n">
         <v>-0.8995</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3133</v>
+        <v>-5.7278</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5657</v>
+        <v>-4.0138</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.7477</v>
+        <v>-1.7139</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9036</v>
+        <v>-4.0559</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1305</v>
+        <v>-2.3175</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7732</v>
+        <v>-1.7384</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1182</v>
+        <v>-2.5517</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4565</v>
+        <v>-0.5239</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3383</v>
+        <v>-2.0277</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0219</v>
+        <v>-1.5043</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.587</v>
+        <v>-1.7936</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5651</v>
+        <v>0.2893</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9308</v>
+        <v>-1.1585</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.433</v>
+        <v>-1.1585</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3244</v>
+        <v>-0.3037</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1086</v>
+        <v>-0.8548</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1698</v>
+        <v>-0.8995</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.741</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-40.6985</v>
+        <v>-40.6983</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.5345</v>
+        <v>-22.5344</v>
       </c>
       <c r="F23" t="n">
         <v>-18.1639</v>
@@ -2218,13 +2218,13 @@
         <v>-23.4484</v>
       </c>
       <c r="I23" t="n">
-        <v>-6.8272</v>
+        <v>-6.827199999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.612000000000002</v>
+        <v>-7.612</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0748</v>
+        <v>2.074800000000001</v>
       </c>
       <c r="L23" t="n">
         <v>-9.6866</v>
@@ -2239,7 +2239,7 @@
         <v>2.8593</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.551115123125783e-17</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.3771</v>
@@ -2248,10 +2248,10 @@
         <v>17.377</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.724299999999999</v>
+        <v>-7.7244</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.8998</v>
+        <v>-2.8997</v>
       </c>
       <c r="U23" t="n">
         <v>-4.8246</v>
@@ -2260,7 +2260,7 @@
         <v>-2.6983</v>
       </c>
       <c r="W23" t="n">
-        <v>5.3541</v>
+        <v>5.354100000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-8.0526</v>
